--- a/public/template/Template Import Pegawai.xlsx
+++ b/public/template/Template Import Pegawai.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evfi2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74F0A64D-FDE9-44E0-A7A5-B2835414B103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBB5F15B-E6BC-42E8-90D5-2ADE4D93EA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{69DB791E-A32B-4FF1-ACDE-63CFAB55E2DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{69DB791E-A32B-4FF1-ACDE-63CFAB55E2DD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Daftar_Pegawai_23-1-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Isi Disini" sheetId="1" r:id="rId1"/>
+    <sheet name="Reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Nama Lengkap*</t>
   </si>
@@ -143,14 +144,107 @@
     <t>Tolong Baca Aturan Dibawah ini:</t>
   </si>
   <si>
-    <t>Setelah membaca ini tolong text yang ada di area kuning dihapus</t>
+    <t>Jabatan*</t>
+  </si>
+  <si>
+    <t>Anggota SDM</t>
+  </si>
+  <si>
+    <t>Direktur</t>
+  </si>
+  <si>
+    <t>Jabatan</t>
+  </si>
+  <si>
+    <t>Anggota Keuangan</t>
+  </si>
+  <si>
+    <t>Anggota Prodi RPL</t>
+  </si>
+  <si>
+    <t>Anggota Prodi SI</t>
+  </si>
+  <si>
+    <t>Dekan Fakultas Bisnis</t>
+  </si>
+  <si>
+    <t>Dekan Fakultas Informatika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekan Fakultas Rekayasa industri </t>
+  </si>
+  <si>
+    <t>Kaprodi Rekayasa Perangkat Lunak</t>
+  </si>
+  <si>
+    <t>Kaprodi Sistem Informasi</t>
+  </si>
+  <si>
+    <t>Kepala Bagian Keuangan</t>
+  </si>
+  <si>
+    <t>Kepala Bagian SDM</t>
+  </si>
+  <si>
+    <t>Kepala Urusan Keuangan</t>
+  </si>
+  <si>
+    <t>Kepala Urusan SDM</t>
+  </si>
+  <si>
+    <t>Wakil Direktur I</t>
+  </si>
+  <si>
+    <t>Wakil Direktur II</t>
+  </si>
+  <si>
+    <t>Wakil Direktur III</t>
+  </si>
+  <si>
+    <t>Status Pegawai</t>
+  </si>
+  <si>
+    <t>TENAGA LEPAS HARIAN</t>
+  </si>
+  <si>
+    <t>PEGAWAI TETAP</t>
+  </si>
+  <si>
+    <t>PEGAWAI PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>OURSOURCING</t>
+  </si>
+  <si>
+    <t>CALON PEGAWAI TETAP</t>
+  </si>
+  <si>
+    <t>TENAGA PERBANTUAN</t>
+  </si>
+  <si>
+    <t>Tipe</t>
+  </si>
+  <si>
+    <t>Dosen</t>
+  </si>
+  <si>
+    <t>TPA</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Perempuan</t>
+  </si>
+  <si>
+    <t>Laki-laki</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,16 +379,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,8 +572,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -602,8 +694,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -646,19 +753,19 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Aksen2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Aksen3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -686,7 +793,6 @@
     <cellStyle name="Baik" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Buruk" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Catatan" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Hipertaut" xfId="42" builtinId="8"/>
     <cellStyle name="Judul" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Judul 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Judul 2" xfId="3" builtinId="17" customBuiltin="1"/>
@@ -1033,247 +1139,414 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B266CB-E729-4D74-B3C3-4EBD7EF425B7}">
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="str">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="str">
         <f>"- Tanda * artinya Wajib Diisi"</f>
         <v>- Tanda * artinya Wajib Diisi</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="str">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="str">
         <f>"- Emergency Contact Boleh Diisi sebutuhnya, jika hanya butuh 1 saja maka hanya isi 1"</f>
         <v>- Emergency Contact Boleh Diisi sebutuhnya, jika hanya butuh 1 saja maka hanya isi 1</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="str">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="str">
         <f>"- Tolong Jangan Hapus Text yang ada di baris pertama atau baris yang berwarna Hijau"</f>
         <v>- Tolong Jangan Hapus Text yang ada di baris pertama atau baris yang berwarna Hijau</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="str">
+        <f>"- Bagian berwarna pink atau Jenis Kelamin, Tipe Pegawai, Status Kepegawaian, Jabatan tolong hanya gunakan nilai yang ada pada dropdown"</f>
+        <v>- Bagian berwarna pink atau Jenis Kelamin, Tipe Pegawai, Status Kepegawaian, Jabatan tolong hanya gunakan nilai yang ada pada dropdown</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H10" xr:uid="{89F2B76A-7297-4BF3-8CB8-3EAD827197F1}">
+      <formula1>"Perempuan, Laki-laki"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L10" xr:uid="{A1E202B2-2A54-4F5C-B15D-8CC33F575B6A}">
+      <formula1>"Dosen, TPA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DAD8753-994F-43FA-A24D-1077A815B91B}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P11</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3FA8265-4FF8-42E6-AA59-8E219D07B3F6}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M10</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F5934F-32A4-4821-AFC8-976511874384}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>